--- a/config/excel/stages.xlsx
+++ b/config/excel/stages.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,21 +423,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,40 +468,65 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>reward_rooms</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>berserker</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>splitter</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>archer</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>fire_mage</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>cross_shooter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>bounce_slime</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>boss_id</t>
         </is>
@@ -517,14 +547,10 @@
           <t>第1关</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -538,7 +564,22 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,14 +596,10 @@
           <t>第2关</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" t="n">
-        <v>12</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -571,12 +608,27 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,14 +645,10 @@
           <t>第3关</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>64</v>
-      </c>
-      <c r="F4" t="n">
-        <v>20</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -609,12 +657,27 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>6</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -631,28 +694,39 @@
           <t>第4关</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>64</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>8</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>14</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -669,11 +743,15 @@
           <t>第5关</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -690,11 +768,22 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>centipede</t>
-        </is>
-      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -711,28 +800,39 @@
           <t>第6关</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>68</v>
-      </c>
-      <c r="F7" t="n">
-        <v>24</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -749,28 +849,39 @@
           <t>第7关</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>72</v>
-      </c>
-      <c r="F8" t="n">
-        <v>28</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -787,28 +898,643 @@
           <t>第8关</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>76</v>
-      </c>
-      <c r="F9" t="n">
-        <v>28</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>第9关</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>第10关</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>lancer_knight</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>第11关</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>第12关</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>第13关</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>第14关</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>第15关</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>第16关</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22</v>
-      </c>
-      <c r="K9" t="n">
-        <v>11</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>第17关</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>第18关</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>第19关</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>第20关</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>centipede</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
